--- a/output/hasil_klasterisasi_SKATER.xlsx
+++ b/output/hasil_klasterisasi_SKATER.xlsx
@@ -773,7 +773,7 @@
         <v>3.384221351570083</v>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -1781,7 +1781,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -1829,7 +1829,7 @@
         <v>0.5545742328652562</v>
       </c>
       <c r="N29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1877,7 +1877,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1925,7 +1925,7 @@
         <v>-0.04323853869210145</v>
       </c>
       <c r="N31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -1973,7 +1973,7 @@
         <v>0.7139909719472184</v>
       </c>
       <c r="N32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2021,7 +2021,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2069,7 +2069,7 @@
         <v>2.148741623684877</v>
       </c>
       <c r="N34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2117,7 +2117,7 @@
         <v>0.9531160805701615</v>
       </c>
       <c r="N35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2165,7 +2165,7 @@
         <v>1.511074667357029</v>
       </c>
       <c r="N36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2213,7 +2213,7 @@
         <v>1.311803743504576</v>
       </c>
       <c r="N37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2261,7 +2261,7 @@
         <v>1.152387004422614</v>
       </c>
       <c r="N38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2357,7 +2357,7 @@
         <v>0.7139909719472184</v>
       </c>
       <c r="N40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2405,7 +2405,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2597,7 +2597,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -2645,7 +2645,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -2693,7 +2693,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -4469,7 +4469,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -4517,7 +4517,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -4565,7 +4565,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -4613,7 +4613,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
@@ -4661,7 +4661,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
@@ -4709,7 +4709,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
@@ -4757,7 +4757,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
@@ -4805,7 +4805,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -4853,7 +4853,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
@@ -4901,7 +4901,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
@@ -4949,7 +4949,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
@@ -4997,7 +4997,7 @@
         <v>1.865966693456853</v>
       </c>
       <c r="N95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
@@ -5045,7 +5045,7 @@
         <v>0.6442461485988599</v>
       </c>
       <c r="N96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
@@ -5093,7 +5093,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
@@ -5621,7 +5621,7 @@
         <v>-0.03185162858687195</v>
       </c>
       <c r="N108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -5861,7 +5861,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114">
@@ -5909,7 +5909,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115">
@@ -5957,7 +5957,7 @@
         <v>2.157938743216641</v>
       </c>
       <c r="N115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116">
@@ -6005,7 +6005,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117">
@@ -6053,7 +6053,7 @@
         <v>0.9316561348631985</v>
       </c>
       <c r="N117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118">
@@ -6101,7 +6101,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119">
@@ -6149,7 +6149,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120">
@@ -6533,7 +6533,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128">
@@ -6629,7 +6629,7 @@
         <v>3.384221351570083</v>
       </c>
       <c r="N129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130">
@@ -7157,7 +7157,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141">
@@ -7205,7 +7205,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="142">
@@ -7253,7 +7253,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="143">
@@ -7301,7 +7301,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N143" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="144">
@@ -7349,7 +7349,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
@@ -7397,7 +7397,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146">
@@ -8213,7 +8213,7 @@
         <v>0.3951574937832942</v>
       </c>
       <c r="N162" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
@@ -8357,7 +8357,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="166">
@@ -8453,7 +8453,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N167" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="168">
@@ -9125,7 +9125,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="182">
@@ -9173,7 +9173,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N182" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
@@ -9269,7 +9269,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N184" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
@@ -10037,7 +10037,7 @@
         <v>0.7272757000712011</v>
       </c>
       <c r="N200" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="201">
@@ -10469,7 +10469,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N209" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="210">
@@ -10517,7 +10517,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N210" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="211">
@@ -10565,7 +10565,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N211" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="212">
@@ -10613,7 +10613,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N212" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="213">
@@ -10661,7 +10661,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N213" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="214">
@@ -10709,7 +10709,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N214" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="215">
@@ -10757,7 +10757,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N215" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="216">
@@ -10805,7 +10805,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N216" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="217">
@@ -10853,7 +10853,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N217" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="218">
@@ -10901,7 +10901,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N218" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="219">
@@ -10949,7 +10949,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N219" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="220">
@@ -10997,7 +10997,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N220" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="221">
@@ -11045,7 +11045,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N221" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="222">
@@ -11093,7 +11093,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N222" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="223">
@@ -11141,7 +11141,7 @@
         <v>0.06303928749538713</v>
       </c>
       <c r="N223" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="224">
@@ -11189,7 +11189,7 @@
         <v>-0.2388863548345227</v>
       </c>
       <c r="N224" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="225">
@@ -11237,7 +11237,7 @@
         <v>0.5944284176357467</v>
       </c>
       <c r="N225" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="226">
@@ -11285,7 +11285,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N226" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="227">
@@ -11333,7 +11333,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N227" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="228">
@@ -11381,7 +11381,7 @@
         <v>-0.3797849878474196</v>
       </c>
       <c r="N228" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="229">
@@ -11429,7 +11429,7 @@
         <v>-0.4019262016265162</v>
       </c>
       <c r="N229" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="230">
@@ -11477,7 +11477,7 @@
         <v>0.1234244157302149</v>
       </c>
       <c r="N230" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="231">
@@ -11621,7 +11621,7 @@
         <v>0.1234244157302149</v>
       </c>
       <c r="N233" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234">
@@ -11717,7 +11717,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N235" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="236">
@@ -11861,7 +11861,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N238" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="239">
@@ -12053,7 +12053,7 @@
         <v>1.743166684479554</v>
       </c>
       <c r="N242" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="243">
@@ -12101,7 +12101,7 @@
         <v>0.9316561348631985</v>
       </c>
       <c r="N243" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="244">
@@ -12149,7 +12149,7 @@
         <v>1.076873812309799</v>
       </c>
       <c r="N244" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="245">
@@ -12629,7 +12629,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N254" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255">
@@ -13301,7 +13301,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N268" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="269">
@@ -13349,7 +13349,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N269" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="270">
@@ -13829,7 +13829,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N279" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="280">
@@ -13877,7 +13877,7 @@
         <v>1.238226786851924</v>
       </c>
       <c r="N280" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="281">
@@ -13925,7 +13925,7 @@
         <v>0.3951574937832942</v>
       </c>
       <c r="N281" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="282">
@@ -13973,7 +13973,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N282" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="283">
@@ -14021,7 +14021,7 @@
         <v>-0.05773096937281016</v>
       </c>
       <c r="N283" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="284">
@@ -14069,7 +14069,7 @@
         <v>-0.1323243635669725</v>
       </c>
       <c r="N284" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="285">
@@ -14117,7 +14117,7 @@
         <v>0.4857351863348068</v>
       </c>
       <c r="N285" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="286">
@@ -14165,7 +14165,7 @@
         <v>1.391512113045557</v>
       </c>
       <c r="N286" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="287">
@@ -14261,7 +14261,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N288" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="289">
@@ -14309,7 +14309,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N289" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="290">
@@ -14357,7 +14357,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N290" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="291">
@@ -14405,7 +14405,7 @@
         <v>-0.6011971254789688</v>
       </c>
       <c r="N291" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
